--- a/docs/assets_output/02_measures_over_time.xlsx
+++ b/docs/assets_output/02_measures_over_time.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
   <si>
     <t>Table 1.1: Route end reasons per quarter</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>To social housing</t>
-  </si>
-  <si>
-    <t>[Not ended]</t>
   </si>
   <si>
     <t>rt_end_yr</t>
@@ -428,15 +425,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -454,9 +451,8 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-    </row>
-    <row r="3" spans="1:15">
+    </row>
+    <row r="3" spans="1:14">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -494,19 +490,16 @@
       <c r="N3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>2017</v>
       </c>
@@ -550,7 +543,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>2018</v>
       </c>
@@ -594,7 +587,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>2</v>
@@ -636,7 +629,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>3</v>
@@ -678,7 +671,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>4</v>
@@ -720,7 +713,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="1">
         <v>2019</v>
       </c>
@@ -764,7 +757,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>2</v>
@@ -806,7 +799,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>3</v>
@@ -848,7 +841,7 @@
         <v>18.1</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>4</v>
@@ -890,7 +883,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14" s="1">
         <v>2020</v>
       </c>
@@ -934,7 +927,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:14">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>2</v>
@@ -976,7 +969,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:14">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>3</v>
@@ -1689,7 +1682,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:14">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>4</v>
@@ -1728,7 +1721,7 @@
         <v>18.6</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:14">
       <c r="A34" s="1">
         <v>2025</v>
       </c>
@@ -1772,523 +1765,488 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:14">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D35">
-        <v>11.5</v>
+        <v>15.8</v>
       </c>
       <c r="E35">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="F35">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="G35">
-        <v>14.8</v>
+        <v>18.4</v>
       </c>
       <c r="H35">
-        <v>27.9</v>
+        <v>5.3</v>
       </c>
       <c r="I35">
-        <v>9.800000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="J35">
+        <v>10.5</v>
+      </c>
+      <c r="K35">
+        <v>2.6</v>
+      </c>
+      <c r="L35">
+        <v>10.5</v>
+      </c>
+      <c r="M35">
+        <v>2.6</v>
+      </c>
+      <c r="N35">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="1">
+        <v>2017</v>
+      </c>
+      <c r="B41">
+        <v>121</v>
+      </c>
+      <c r="C41">
+        <v>14.9</v>
+      </c>
+      <c r="D41">
+        <v>4.1</v>
+      </c>
+      <c r="E41">
+        <v>1.7</v>
+      </c>
+      <c r="F41">
+        <v>17.4</v>
+      </c>
+      <c r="G41">
+        <v>1.7</v>
+      </c>
+      <c r="H41">
         <v>6.6</v>
       </c>
-      <c r="K35">
-        <v>4.9</v>
-      </c>
-      <c r="L35">
-        <v>6.6</v>
-      </c>
-      <c r="M35">
+      <c r="I41">
         <v>3.3</v>
       </c>
-      <c r="N35">
-        <v>8.199999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1">
-        <v>4</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37">
-        <v>738</v>
-      </c>
-      <c r="O37">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
-      <c r="A39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:15">
-      <c r="A41" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="J41">
+        <v>4.1</v>
+      </c>
+      <c r="K41">
+        <v>11.6</v>
+      </c>
+      <c r="L41">
+        <v>5.8</v>
+      </c>
+      <c r="M41">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="1">
+        <v>2018</v>
+      </c>
+      <c r="B42">
+        <v>668</v>
+      </c>
+      <c r="C42">
+        <v>13</v>
+      </c>
+      <c r="D42">
+        <v>7.6</v>
+      </c>
+      <c r="E42">
+        <v>2.5</v>
+      </c>
+      <c r="F42">
+        <v>15.1</v>
+      </c>
+      <c r="G42">
+        <v>3.4</v>
+      </c>
+      <c r="H42">
+        <v>6.3</v>
+      </c>
+      <c r="I42">
+        <v>3.9</v>
+      </c>
+      <c r="J42">
         <v>6</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
-      <c r="A42" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="K42">
+        <v>11.1</v>
+      </c>
+      <c r="L42">
+        <v>4.5</v>
+      </c>
+      <c r="M42">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="1">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B43">
-        <v>121</v>
+        <v>649</v>
       </c>
       <c r="C43">
-        <v>14.9</v>
+        <v>15.4</v>
       </c>
       <c r="D43">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="E43">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="F43">
-        <v>17.4</v>
+        <v>19.6</v>
       </c>
       <c r="G43">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="H43">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="I43">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J43">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="K43">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="L43">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="M43">
-        <v>28.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="1">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B44">
-        <v>668</v>
+        <v>635</v>
       </c>
       <c r="C44">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="D44">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="E44">
         <v>2.5</v>
       </c>
       <c r="F44">
-        <v>15.1</v>
+        <v>15.9</v>
       </c>
       <c r="G44">
+        <v>0.8</v>
+      </c>
+      <c r="H44">
+        <v>6</v>
+      </c>
+      <c r="I44">
+        <v>3.1</v>
+      </c>
+      <c r="J44">
+        <v>3.1</v>
+      </c>
+      <c r="K44">
+        <v>7.7</v>
+      </c>
+      <c r="L44">
+        <v>10.1</v>
+      </c>
+      <c r="M44">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B45">
+        <v>595</v>
+      </c>
+      <c r="C45">
+        <v>13.9</v>
+      </c>
+      <c r="D45">
+        <v>9.6</v>
+      </c>
+      <c r="E45">
         <v>3.4</v>
       </c>
-      <c r="H44">
-        <v>6.3</v>
-      </c>
-      <c r="I44">
+      <c r="F45">
+        <v>18.8</v>
+      </c>
+      <c r="G45">
+        <v>1.3</v>
+      </c>
+      <c r="H45">
+        <v>7.4</v>
+      </c>
+      <c r="I45">
+        <v>4.4</v>
+      </c>
+      <c r="J45">
+        <v>4.2</v>
+      </c>
+      <c r="K45">
+        <v>7.9</v>
+      </c>
+      <c r="L45">
+        <v>6.6</v>
+      </c>
+      <c r="M45">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="1">
+        <v>2022</v>
+      </c>
+      <c r="B46">
+        <v>540</v>
+      </c>
+      <c r="C46">
+        <v>14.1</v>
+      </c>
+      <c r="D46">
+        <v>7.4</v>
+      </c>
+      <c r="E46">
+        <v>2.4</v>
+      </c>
+      <c r="F46">
+        <v>22.4</v>
+      </c>
+      <c r="G46">
+        <v>0.9</v>
+      </c>
+      <c r="H46">
+        <v>7.4</v>
+      </c>
+      <c r="I46">
+        <v>2.4</v>
+      </c>
+      <c r="J46">
+        <v>3.5</v>
+      </c>
+      <c r="K46">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L46">
+        <v>6.5</v>
+      </c>
+      <c r="M46">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="1">
+        <v>2023</v>
+      </c>
+      <c r="B47">
+        <v>493</v>
+      </c>
+      <c r="C47">
+        <v>19.9</v>
+      </c>
+      <c r="D47">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E47">
+        <v>2.8</v>
+      </c>
+      <c r="F47">
+        <v>27</v>
+      </c>
+      <c r="G47">
+        <v>2.4</v>
+      </c>
+      <c r="H47">
+        <v>5.5</v>
+      </c>
+      <c r="I47">
         <v>3.9</v>
       </c>
-      <c r="J44">
-        <v>6</v>
-      </c>
-      <c r="K44">
-        <v>11.1</v>
-      </c>
-      <c r="L44">
-        <v>4.5</v>
-      </c>
-      <c r="M44">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
-      <c r="A45" s="1">
-        <v>2019</v>
-      </c>
-      <c r="B45">
-        <v>649</v>
-      </c>
-      <c r="C45">
-        <v>15.4</v>
-      </c>
-      <c r="D45">
-        <v>6.8</v>
-      </c>
-      <c r="E45">
-        <v>2.6</v>
-      </c>
-      <c r="F45">
-        <v>19.6</v>
-      </c>
-      <c r="G45">
-        <v>2.3</v>
-      </c>
-      <c r="H45">
-        <v>4.6</v>
-      </c>
-      <c r="I45">
-        <v>4.8</v>
-      </c>
-      <c r="J45">
-        <v>2.5</v>
-      </c>
-      <c r="K45">
-        <v>11.2</v>
-      </c>
-      <c r="L45">
-        <v>6.5</v>
-      </c>
-      <c r="M45">
-        <v>23.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
-      <c r="A46" s="1">
-        <v>2020</v>
-      </c>
-      <c r="B46">
-        <v>635</v>
-      </c>
-      <c r="C46">
-        <v>13.1</v>
-      </c>
-      <c r="D46">
-        <v>9.6</v>
-      </c>
-      <c r="E46">
-        <v>2.5</v>
-      </c>
-      <c r="F46">
-        <v>15.9</v>
-      </c>
-      <c r="G46">
-        <v>0.8</v>
-      </c>
-      <c r="H46">
-        <v>6</v>
-      </c>
-      <c r="I46">
-        <v>3.1</v>
-      </c>
-      <c r="J46">
-        <v>3.1</v>
-      </c>
-      <c r="K46">
-        <v>7.7</v>
-      </c>
-      <c r="L46">
-        <v>10.1</v>
-      </c>
-      <c r="M46">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
-      <c r="A47" s="1">
-        <v>2021</v>
-      </c>
-      <c r="B47">
-        <v>595</v>
-      </c>
-      <c r="C47">
-        <v>13.9</v>
-      </c>
-      <c r="D47">
-        <v>9.6</v>
-      </c>
-      <c r="E47">
-        <v>3.4</v>
-      </c>
-      <c r="F47">
-        <v>18.8</v>
-      </c>
-      <c r="G47">
-        <v>1.3</v>
-      </c>
-      <c r="H47">
-        <v>7.4</v>
-      </c>
-      <c r="I47">
-        <v>4.4</v>
-      </c>
       <c r="J47">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K47">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="L47">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="M47">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B48">
-        <v>540</v>
+        <v>455</v>
       </c>
       <c r="C48">
-        <v>14.1</v>
+        <v>17.4</v>
       </c>
       <c r="D48">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="E48">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="F48">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="G48">
         <v>0.9</v>
       </c>
       <c r="H48">
-        <v>7.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I48">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J48">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K48">
-        <v>9.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="L48">
+        <v>7.3</v>
+      </c>
+      <c r="M48">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B49">
+        <v>154</v>
+      </c>
+      <c r="C49">
+        <v>9.1</v>
+      </c>
+      <c r="D49">
         <v>6.5</v>
       </c>
-      <c r="M48">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="1">
-        <v>2023</v>
-      </c>
-      <c r="B49">
-        <v>493</v>
-      </c>
-      <c r="C49">
-        <v>19.9</v>
-      </c>
-      <c r="D49">
-        <v>8.300000000000001</v>
-      </c>
       <c r="E49">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="F49">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G49">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="H49">
-        <v>5.5</v>
+        <v>9.1</v>
       </c>
       <c r="I49">
+        <v>5.2</v>
+      </c>
+      <c r="J49">
         <v>3.9</v>
       </c>
-      <c r="J49">
-        <v>3.2</v>
-      </c>
       <c r="K49">
-        <v>7.1</v>
+        <v>10.4</v>
       </c>
       <c r="L49">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="M49">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="1">
-        <v>2024</v>
-      </c>
-      <c r="B50">
-        <v>455</v>
-      </c>
-      <c r="C50">
-        <v>17.4</v>
-      </c>
-      <c r="D50">
-        <v>5.7</v>
-      </c>
-      <c r="E50">
-        <v>3.3</v>
-      </c>
-      <c r="F50">
-        <v>24</v>
-      </c>
-      <c r="G50">
-        <v>0.9</v>
-      </c>
-      <c r="H50">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="I50">
-        <v>5.3</v>
-      </c>
-      <c r="J50">
-        <v>4</v>
-      </c>
-      <c r="K50">
-        <v>3.3</v>
-      </c>
-      <c r="L50">
-        <v>7.3</v>
-      </c>
-      <c r="M50">
-        <v>19.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B51">
-        <v>178</v>
-      </c>
-      <c r="C51">
-        <v>8.4</v>
-      </c>
-      <c r="D51">
-        <v>6.2</v>
-      </c>
-      <c r="E51">
-        <v>1.7</v>
-      </c>
-      <c r="F51">
-        <v>23.6</v>
-      </c>
-      <c r="G51">
-        <v>11.8</v>
-      </c>
-      <c r="H51">
-        <v>9</v>
-      </c>
-      <c r="I51">
-        <v>4.5</v>
-      </c>
-      <c r="J51">
-        <v>4.5</v>
-      </c>
-      <c r="K51">
-        <v>9</v>
-      </c>
-      <c r="L51">
-        <v>5.1</v>
-      </c>
-      <c r="M51">
-        <v>16.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52" s="1"/>
-      <c r="B52">
-        <v>738</v>
-      </c>
-      <c r="N52">
-        <v>100</v>
+        <v>18.8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="D2:O2"/>
+    <mergeCell ref="D2:N2"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
@@ -2296,8 +2254,8 @@
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="C40:N40"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C38:M38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
